--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74222702</v>
       </c>
       <c r="B2" t="n">
-        <v>101854</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566826.4893019535</v>
+        <v>566826</v>
       </c>
       <c r="R2" t="n">
-        <v>6446717.486268888</v>
+        <v>6446717</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1981-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1981-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222702</v>
       </c>
       <c r="B2" t="n">
-        <v>104223</v>
+        <v>104232</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222702</v>
       </c>
       <c r="B2" t="n">
-        <v>104232</v>
+        <v>104235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222702</v>
       </c>
       <c r="B2" t="n">
-        <v>104235</v>
+        <v>104262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222702</v>
       </c>
       <c r="B2" t="n">
-        <v>104262</v>
+        <v>104268</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222702</v>
       </c>
       <c r="B2" t="n">
-        <v>104268</v>
+        <v>104275</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222702</v>
       </c>
       <c r="B2" t="n">
-        <v>104275</v>
+        <v>104279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222702</v>
       </c>
       <c r="B2" t="n">
-        <v>104279</v>
+        <v>104286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222702</v>
       </c>
       <c r="B2" t="n">
-        <v>104289</v>
+        <v>104294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222702</v>
       </c>
       <c r="B2" t="n">
-        <v>104294</v>
+        <v>104302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74222702</v>
       </c>
       <c r="B2" t="n">
-        <v>104302</v>
+        <v>104312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74222702</v>
+        <v>98632409</v>
       </c>
       <c r="B2" t="n">
-        <v>104312</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220461</v>
+        <v>100067</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>With.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kvistrum 700 m SV ladugård, Sm</t>
+          <t>Åtvidaberg-Falerum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566826</v>
+        <v>566820</v>
       </c>
       <c r="R2" t="n">
-        <v>6446717</v>
+        <v>6446713</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +749,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1981-01-01</t>
+          <t>2021-03-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1981-12-31</t>
+          <t>2021-03-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7G9d 3144. SOM: Cardamine flexuosa. LEG: Erik Moberger</t>
+          <t>Förbiflygande Kom från NV på hög höjd, flög i ganska hög fart först, började cirkulera några varv och fortsatta sen mot SO tills den försvann bakom skymmande träd. Ålder svårbestämd pga dåligt ljus, men tyckte mig se vit stjärt och ljusare huvud, såg AXN0071 (Calluna AB) spelflyktsinventering</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,43 +781,29 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Skogsvägskant i dalgång</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Josefina Pehrson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>98632409</v>
+        <v>98632420</v>
       </c>
       <c r="B3" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -835,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566820.7455559814</v>
+        <v>566937</v>
       </c>
       <c r="R3" t="n">
-        <v>6446713.167319786</v>
+        <v>6446522</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,27 +870,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2021-03-23</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Förbiflygande Kom från NV på hög höjd, flög i ganska hög fart först, började cirkulera några varv och fortsatta sen mot SO tills den försvann bakom skymmande träd. Ålder svårbestämd pga dåligt ljus, men tyckte mig se vit stjärt och ljusare huvud, såg AXN0071 (Calluna AB) spelflyktsinventering</t>
+          <t>Kretsande Kretsade fram och tillbaka över området, försvann allt mer bortåt, tappade bort den i värmedallret. AXN0071 (Calluna AB) spelflyktsinventering</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -915,16 +920,11 @@
         <v>98632511</v>
       </c>
       <c r="B4" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -961,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>567049.2214261909</v>
+        <v>567050</v>
       </c>
       <c r="R4" t="n">
-        <v>6446459.983302006</v>
+        <v>6446460</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1038,62 +1038,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>98632420</v>
+        <v>74222702</v>
       </c>
       <c r="B5" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100067</v>
+        <v>220461</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Åtvidaberg-Falerum, Sm</t>
+          <t>Kvistrum 700 m SV ladugård, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566936.607511775</v>
+        <v>566826</v>
       </c>
       <c r="R5" t="n">
-        <v>6446521.419714986</v>
+        <v>6446717</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1117,27 +1103,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:02</t>
+          <t>1981-01-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2021-03-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:16</t>
+          <t>1981-12-31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Kretsande Kretsade fram och tillbaka över området, försvann allt mer bortåt, tappade bort den i värmedallret. AXN0071 (Calluna AB) spelflyktsinventering</t>
+          <t>Smålands flora 2007: KOO: 7G9d 3144. SOM: Cardamine flexuosa. LEG: Erik Moberger</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,18 +1125,27 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogsvägskant i dalgång</t>
+        </is>
+      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Josefina Pehrson</t>
+          <t>Margareta Edqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Julia Svensson</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53205-2022 artfynd.xlsx
+++ b/artfynd/A 53205-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98632409</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98632420</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1035,6 +1050,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98632511</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1146,8 +1166,19 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74222702</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>